--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125723948</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125723948</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125723948</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125723948</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +769,210 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128582699</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100726</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>788600</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7370175</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växtplats 4</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128582698</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100726</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvarnronningen, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>788623</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7370195</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växtplats 5</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100726</v>
+        <v>100734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100726</v>
+        <v>100734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100734</v>
+        <v>100741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100734</v>
+        <v>100741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100741</v>
+        <v>100746</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100741</v>
+        <v>100746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100746</v>
+        <v>100752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100746</v>
+        <v>100752</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100752</v>
+        <v>100753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100752</v>
+        <v>100753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100753</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100753</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100786</v>
+        <v>100793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100786</v>
+        <v>100793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100793</v>
+        <v>100797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100793</v>
+        <v>100797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100797</v>
+        <v>100804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100797</v>
+        <v>100804</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23096-2025 artfynd.xlsx
+++ b/artfynd/A 23096-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128582699</v>
       </c>
       <c r="B3" t="n">
-        <v>100812</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128582698</v>
       </c>
       <c r="B4" t="n">
-        <v>100812</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
